--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.47106358581915</v>
+        <v>13.72654783269561</v>
       </c>
       <c r="D2" t="n">
-        <v>71.59510979218935</v>
+        <v>11.63420534123077</v>
       </c>
       <c r="E2" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F2" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>97.88670569823783</v>
+        <v>15.90658967596365</v>
       </c>
       <c r="D3" t="n">
-        <v>79.23940047534221</v>
+        <v>12.87640257724311</v>
       </c>
       <c r="E3" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F3" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.93244026289164</v>
+        <v>4.864021542719891</v>
       </c>
       <c r="D4" t="n">
-        <v>3.044430137290624</v>
+        <v>0.4947198973097263</v>
       </c>
       <c r="E4" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F4" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>82.32143204838893</v>
+        <v>13.3772327078632</v>
       </c>
       <c r="D5" t="n">
-        <v>76.4543198418132</v>
+        <v>12.42382697429464</v>
       </c>
       <c r="E5" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F5" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.39526465632608</v>
+        <v>4.289230506652988</v>
       </c>
       <c r="D6" t="n">
-        <v>4.548488195542046</v>
+        <v>0.7391293317755826</v>
       </c>
       <c r="E6" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F6" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.26312806560364</v>
+        <v>5.242758310660592</v>
       </c>
       <c r="D7" t="n">
-        <v>8.358103350657656</v>
+        <v>1.358191794481869</v>
       </c>
       <c r="E7" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F7" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>84.49496871189295</v>
+        <v>13.73043241568261</v>
       </c>
       <c r="D8" t="n">
-        <v>72.34457588620884</v>
+        <v>11.75599358150894</v>
       </c>
       <c r="E8" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F8" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.01093687115241</v>
+        <v>7.639277241562267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.67468234325046</v>
+        <v>4.497135880778201</v>
       </c>
       <c r="E9" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F9" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.22777098018224</v>
+        <v>3.774512784279614</v>
       </c>
       <c r="D10" t="n">
-        <v>8.218854004110122</v>
+        <v>1.335563775667895</v>
       </c>
       <c r="E10" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F10" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.33534832401216</v>
+        <v>5.416994102651976</v>
       </c>
       <c r="D11" t="n">
-        <v>15.83411700990265</v>
+        <v>2.57304401410918</v>
       </c>
       <c r="E11" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F11" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.58534753129025</v>
+        <v>2.857618973834666</v>
       </c>
       <c r="D12" t="n">
-        <v>6.938227151747166</v>
+        <v>1.127461912158915</v>
       </c>
       <c r="E12" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F12" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>98.12913001310797</v>
+        <v>15.94598362713005</v>
       </c>
       <c r="D13" t="n">
-        <v>72.76479863934894</v>
+        <v>11.8242797788942</v>
       </c>
       <c r="E13" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F13" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>80.06592977688614</v>
+        <v>13.010713588744</v>
       </c>
       <c r="D14" t="n">
-        <v>66.37234653674007</v>
+        <v>10.78550631222026</v>
       </c>
       <c r="E14" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F14" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>71.60495800923889</v>
+        <v>11.63580567650132</v>
       </c>
       <c r="D15" t="n">
-        <v>67.94796587060227</v>
+        <v>11.04154445397287</v>
       </c>
       <c r="E15" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F15" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>65.81219843164843</v>
+        <v>10.69448224514287</v>
       </c>
       <c r="D16" t="n">
-        <v>57.54357105224219</v>
+        <v>9.350830295989356</v>
       </c>
       <c r="E16" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F16" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>12.01093765239739</v>
+        <v>1.951777368514575</v>
       </c>
       <c r="D17" t="n">
-        <v>9.448179554062953</v>
+        <v>1.53532917753523</v>
       </c>
       <c r="E17" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F17" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>91.66406958751874</v>
+        <v>14.89541130797179</v>
       </c>
       <c r="D18" t="n">
-        <v>68.14194742998785</v>
+        <v>11.07306645737303</v>
       </c>
       <c r="E18" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F18" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>57.60039873417932</v>
+        <v>9.36006479430414</v>
       </c>
       <c r="D19" t="n">
-        <v>42.52438235376188</v>
+        <v>6.910212132486306</v>
       </c>
       <c r="E19" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F19" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>83.18834778518953</v>
+        <v>13.5181065150933</v>
       </c>
       <c r="D20" t="n">
-        <v>62.75358971783425</v>
+        <v>10.19745832914806</v>
       </c>
       <c r="E20" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F20" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>10.88905404406335</v>
+        <v>1.769471282160295</v>
       </c>
       <c r="D21" t="n">
-        <v>2.420593595877133</v>
+        <v>0.3933464593300341</v>
       </c>
       <c r="E21" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F21" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>39.01788005931508</v>
+        <v>6.3404055096387</v>
       </c>
       <c r="D22" t="n">
-        <v>24.28172947271804</v>
+        <v>3.945781039316683</v>
       </c>
       <c r="E22" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F22" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>55.45609640733228</v>
+        <v>9.011615666191496</v>
       </c>
       <c r="D23" t="n">
-        <v>45.49152985874282</v>
+        <v>7.392373602045708</v>
       </c>
       <c r="E23" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F23" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>60.86348888003463</v>
+        <v>9.890316943005628</v>
       </c>
       <c r="D24" t="n">
-        <v>61.11091440541543</v>
+        <v>9.930523590880007</v>
       </c>
       <c r="E24" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F24" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>69.71804675969123</v>
+        <v>11.32918259844983</v>
       </c>
       <c r="D25" t="n">
-        <v>54.3407928118122</v>
+        <v>8.830378831919482</v>
       </c>
       <c r="E25" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F25" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>10.13506450824255</v>
+        <v>1.646947982589415</v>
       </c>
       <c r="D26" t="n">
-        <v>6.489419807998588</v>
+        <v>1.054530718799771</v>
       </c>
       <c r="E26" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F26" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>52.23056935075453</v>
+        <v>8.487467519497612</v>
       </c>
       <c r="D27" t="n">
-        <v>37.5292232416264</v>
+        <v>6.09849877676429</v>
       </c>
       <c r="E27" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F27" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>17.46844248225404</v>
+        <v>2.838621903366283</v>
       </c>
       <c r="D28" t="n">
-        <v>7.140558062535761</v>
+        <v>1.160340685162061</v>
       </c>
       <c r="E28" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F28" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>5.657213883417424</v>
+        <v>0.9192972560553314</v>
       </c>
       <c r="D29" t="n">
-        <v>11.34986937344698</v>
+        <v>1.844353773185135</v>
       </c>
       <c r="E29" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F29" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>84.98737348024846</v>
+        <v>13.81044819054038</v>
       </c>
       <c r="D30" t="n">
-        <v>53.8770125593819</v>
+        <v>8.755014540899559</v>
       </c>
       <c r="E30" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F30" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>43.97595622050572</v>
+        <v>7.14609288583218</v>
       </c>
       <c r="D31" t="n">
-        <v>41.80360092527977</v>
+        <v>6.793085150357964</v>
       </c>
       <c r="E31" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F31" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>66.75736734150382</v>
+        <v>10.84807219299437</v>
       </c>
       <c r="D32" t="n">
-        <v>41.88771680208051</v>
+        <v>6.806753980338083</v>
       </c>
       <c r="E32" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F32" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>42.03044022796752</v>
+        <v>6.829946537044722</v>
       </c>
       <c r="D33" t="n">
-        <v>26.28372784624828</v>
+        <v>4.271105775015346</v>
       </c>
       <c r="E33" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F33" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>79.16050219879389</v>
+        <v>12.86358160730401</v>
       </c>
       <c r="D34" t="n">
-        <v>43.71049330964845</v>
+        <v>7.102955162817874</v>
       </c>
       <c r="E34" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F34" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>41.20047238680251</v>
+        <v>6.695076762855408</v>
       </c>
       <c r="D35" t="n">
-        <v>30.64924504050151</v>
+        <v>4.980502319081496</v>
       </c>
       <c r="E35" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F35" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>36.46574337854106</v>
+        <v>5.925683299012923</v>
       </c>
       <c r="D36" t="n">
-        <v>38.11006932710264</v>
+        <v>6.19288626565418</v>
       </c>
       <c r="E36" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F36" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>27.17160019624488</v>
+        <v>4.415385031889794</v>
       </c>
       <c r="D37" t="n">
-        <v>27.47662738767866</v>
+        <v>4.464951950497783</v>
       </c>
       <c r="E37" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F37" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>26.26880064289977</v>
+        <v>4.268680104471212</v>
       </c>
       <c r="D38" t="n">
-        <v>9.869479141948037</v>
+        <v>1.603790360566556</v>
       </c>
       <c r="E38" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F38" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>57.7092171085826</v>
+        <v>9.377747780144674</v>
       </c>
       <c r="D39" t="n">
-        <v>29.85610609618826</v>
+        <v>4.851617240630593</v>
       </c>
       <c r="E39" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F39" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>76.73515192747821</v>
+        <v>12.46946218821521</v>
       </c>
       <c r="D40" t="n">
-        <v>36.41033675479402</v>
+        <v>5.916679722654028</v>
       </c>
       <c r="E40" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F40" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>33.15090121072878</v>
+        <v>5.387021446743426</v>
       </c>
       <c r="D41" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E41" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F41" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>18.8719113028056</v>
+        <v>3.06668558670591</v>
       </c>
       <c r="D42" t="n">
-        <v>20.76802722952656</v>
+        <v>3.374804424798067</v>
       </c>
       <c r="E42" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F42" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>18.87071849184003</v>
+        <v>3.066491754924005</v>
       </c>
       <c r="D43" t="n">
-        <v>19.61162481751694</v>
+        <v>3.186889032846502</v>
       </c>
       <c r="E43" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F43" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>33.04289671236292</v>
+        <v>5.369470715758974</v>
       </c>
       <c r="D44" t="n">
-        <v>0.854715277020542</v>
+        <v>0.1388912325158381</v>
       </c>
       <c r="E44" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F44" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>47.71884583153502</v>
+        <v>7.754312447624441</v>
       </c>
       <c r="D45" t="n">
-        <v>14.00805806615906</v>
+        <v>2.276309435750848</v>
       </c>
       <c r="E45" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F45" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>39.24847427503095</v>
+        <v>6.37787706969253</v>
       </c>
       <c r="D46" t="n">
-        <v>17.37914537247304</v>
+        <v>2.824111123026869</v>
       </c>
       <c r="E46" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F46" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>35.44677590567032</v>
+        <v>5.760101084671428</v>
       </c>
       <c r="D47" t="n">
-        <v>14.88693334018483</v>
+        <v>2.419126667780036</v>
       </c>
       <c r="E47" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F47" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>16.55224741462483</v>
+        <v>2.689740204876535</v>
       </c>
       <c r="D48" t="n">
-        <v>15.5263384752201</v>
+        <v>2.523030002223266</v>
       </c>
       <c r="E48" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F48" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>19.6645423526628</v>
+        <v>3.195488132307706</v>
       </c>
       <c r="D49" t="n">
-        <v>21.66093700781827</v>
+        <v>3.519902263770468</v>
       </c>
       <c r="E49" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F49" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>11.22091005489779</v>
+        <v>1.823397883920891</v>
       </c>
       <c r="D50" t="n">
-        <v>13.22235593249448</v>
+        <v>2.148632839030353</v>
       </c>
       <c r="E50" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F50" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>47.66252526792024</v>
+        <v>7.74516035603704</v>
       </c>
       <c r="D51" t="n">
-        <v>18.84084077286794</v>
+        <v>3.061636625591041</v>
       </c>
       <c r="E51" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F51" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>13.45245486515321</v>
+        <v>2.186023915587396</v>
       </c>
       <c r="D52" t="n">
-        <v>15.36346187480855</v>
+        <v>2.49656255465639</v>
       </c>
       <c r="E52" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F52" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>57.2780665763079</v>
+        <v>9.307685818650034</v>
       </c>
       <c r="D53" t="n">
-        <v>13.60099190528411</v>
+        <v>2.210161184608668</v>
       </c>
       <c r="E53" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F53" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>9.31074252326427</v>
+        <v>1.512995660030444</v>
       </c>
       <c r="D54" t="n">
-        <v>7.988702534853789</v>
+        <v>1.298164161913741</v>
       </c>
       <c r="E54" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F54" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>53.92078921232388</v>
+        <v>8.76212824700263</v>
       </c>
       <c r="D55" t="n">
-        <v>8.167761245506975</v>
+        <v>1.327261202394884</v>
       </c>
       <c r="E55" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F55" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>36.3930945244749</v>
+        <v>5.913877860227171</v>
       </c>
       <c r="D56" t="n">
-        <v>33.3582717264084</v>
+        <v>5.420719155541365</v>
       </c>
       <c r="E56" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F56" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>3.523271188107872</v>
+        <v>0.5725315680675291</v>
       </c>
       <c r="D57" t="n">
-        <v>5.217317734657281</v>
+        <v>0.8478141318818082</v>
       </c>
       <c r="E57" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F57" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>40.3922369243897</v>
+        <v>6.563738500213327</v>
       </c>
       <c r="D58" t="n">
-        <v>32.93331670823076</v>
+        <v>5.351663965087498</v>
       </c>
       <c r="E58" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F58" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>22.02689610151456</v>
+        <v>3.579370616496117</v>
       </c>
       <c r="D59" t="n">
-        <v>22.01588044288115</v>
+        <v>3.577580571968187</v>
       </c>
       <c r="E59" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F59" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>14.85531638725609</v>
+        <v>2.413988912929114</v>
       </c>
       <c r="D60" t="n">
-        <v>12.86636941071104</v>
+        <v>2.090785029240543</v>
       </c>
       <c r="E60" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F60" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>75.7147438268409</v>
+        <v>12.30364587186165</v>
       </c>
       <c r="D61" t="n">
-        <v>32.19624276682695</v>
+        <v>5.23188944960938</v>
       </c>
       <c r="E61" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F61" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>66.94120246397705</v>
+        <v>10.87794540039627</v>
       </c>
       <c r="D62" t="n">
-        <v>23.90194296593343</v>
+        <v>3.884065731964182</v>
       </c>
       <c r="E62" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F62" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>44.79155334790057</v>
+        <v>7.278627419033842</v>
       </c>
       <c r="D63" t="n">
-        <v>6.58251734153164</v>
+        <v>1.069659067998892</v>
       </c>
       <c r="E63" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F63" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>49.90360251427737</v>
+        <v>8.109335408570074</v>
       </c>
       <c r="D64" t="n">
-        <v>27.30601228062399</v>
+        <v>4.437226995601399</v>
       </c>
       <c r="E64" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F64" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>62.86715060211573</v>
+        <v>10.21591197284381</v>
       </c>
       <c r="D65" t="n">
-        <v>17.5739117708429</v>
+        <v>2.855760662761972</v>
       </c>
       <c r="E65" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F65" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>17.68400840085269</v>
+        <v>2.873651365138562</v>
       </c>
       <c r="D66" t="n">
-        <v>15.82747988160373</v>
+        <v>2.571965480760606</v>
       </c>
       <c r="E66" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F66" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>34.59148662183518</v>
+        <v>5.621116576048217</v>
       </c>
       <c r="D67" t="n">
-        <v>32.58355065509478</v>
+        <v>5.294826981452903</v>
       </c>
       <c r="E67" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F67" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>74.17287488621628</v>
+        <v>12.05309216901015</v>
       </c>
       <c r="D68" t="n">
-        <v>33.6262273739087</v>
+        <v>5.464261948260163</v>
       </c>
       <c r="E68" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F68" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>71.78719668597769</v>
+        <v>11.66541946147137</v>
       </c>
       <c r="D69" t="n">
-        <v>27.91276733277913</v>
+        <v>4.535824691576608</v>
       </c>
       <c r="E69" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F69" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>32.42030442274944</v>
+        <v>5.268299468696784</v>
       </c>
       <c r="D70" t="n">
-        <v>10.81349858566989</v>
+        <v>1.757193520171357</v>
       </c>
       <c r="E70" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F70" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>26.65697741630923</v>
+        <v>4.33175883015025</v>
       </c>
       <c r="D71" t="n">
-        <v>24.79249559921855</v>
+        <v>4.028780534873015</v>
       </c>
       <c r="E71" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F71" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>34.6359896499273</v>
+        <v>5.628348318113185</v>
       </c>
       <c r="D72" t="n">
-        <v>32.69422673728609</v>
+        <v>5.312811844808991</v>
       </c>
       <c r="E72" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F72" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>27.2510037593781</v>
+        <v>4.428288110898942</v>
       </c>
       <c r="D73" t="n">
-        <v>26.49465628125164</v>
+        <v>4.305381645703392</v>
       </c>
       <c r="E73" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F73" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>57.93361579566886</v>
+        <v>9.41421256679619</v>
       </c>
       <c r="D74" t="n">
-        <v>35.3537038377262</v>
+        <v>5.744976873630508</v>
       </c>
       <c r="E74" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F74" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>43.69373436769291</v>
+        <v>7.100231834750098</v>
       </c>
       <c r="D75" t="n">
-        <v>2.088509801284762</v>
+        <v>0.3393828427087738</v>
       </c>
       <c r="E75" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F75" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>26.77822096249075</v>
+        <v>4.351460906404746</v>
       </c>
       <c r="D76" t="n">
-        <v>25.26251040472422</v>
+        <v>4.105157940767686</v>
       </c>
       <c r="E76" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F76" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>42.099564742622</v>
+        <v>6.841179270676076</v>
       </c>
       <c r="D77" t="n">
-        <v>40.1350230509701</v>
+        <v>6.521941245782642</v>
       </c>
       <c r="E77" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F77" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>65.36705070610226</v>
+        <v>10.62214573974162</v>
       </c>
       <c r="D78" t="n">
-        <v>29.09267052245865</v>
+        <v>4.727558959899531</v>
       </c>
       <c r="E78" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F78" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>50.39388413884218</v>
+        <v>8.189006172561855</v>
       </c>
       <c r="D79" t="n">
-        <v>46.70001938910831</v>
+        <v>7.588753150730101</v>
       </c>
       <c r="E79" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F79" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>67.53991720603304</v>
+        <v>10.97523654598037</v>
       </c>
       <c r="D80" t="n">
-        <v>36.3532687691217</v>
+        <v>5.907406174982276</v>
       </c>
       <c r="E80" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F80" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>30.73653552531539</v>
+        <v>4.994687022863752</v>
       </c>
       <c r="D81" t="n">
-        <v>15.63326294242822</v>
+        <v>2.540405228144585</v>
       </c>
       <c r="E81" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F81" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>36.02620072083153</v>
+        <v>5.854257617135123</v>
       </c>
       <c r="D82" t="n">
-        <v>9.323016233835606</v>
+        <v>1.514990137998286</v>
       </c>
       <c r="E82" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F82" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>27.88658821087954</v>
+        <v>4.531570584267926</v>
       </c>
       <c r="D83" t="n">
-        <v>27.89981053261106</v>
+        <v>4.533719211549298</v>
       </c>
       <c r="E83" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F83" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>50.71520269695166</v>
+        <v>8.241220438254645</v>
       </c>
       <c r="D84" t="n">
-        <v>11.18756681386315</v>
+        <v>1.817979607252763</v>
       </c>
       <c r="E84" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F84" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>34.05791230335102</v>
+        <v>5.53441074929454</v>
       </c>
       <c r="D85" t="n">
-        <v>33.24790849824618</v>
+        <v>5.402785130965005</v>
       </c>
       <c r="E85" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F85" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>40.88070474024141</v>
+        <v>6.643114520289228</v>
       </c>
       <c r="D86" t="n">
-        <v>39.36395745710842</v>
+        <v>6.396643086780118</v>
       </c>
       <c r="E86" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F86" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>29.40006865380748</v>
+        <v>4.777511156243715</v>
       </c>
       <c r="D87" t="n">
-        <v>28.10632185552843</v>
+        <v>4.56727730152337</v>
       </c>
       <c r="E87" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F87" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>73.0145223205644</v>
+        <v>11.86485987709171</v>
       </c>
       <c r="D88" t="n">
-        <v>53.40952825460069</v>
+        <v>8.679048341372612</v>
       </c>
       <c r="E88" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F88" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>21.61388322403839</v>
+        <v>3.512256023906238</v>
       </c>
       <c r="D89" t="n">
-        <v>20.29631853591875</v>
+        <v>3.298151762086797</v>
       </c>
       <c r="E89" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F89" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>72.04660160894015</v>
+        <v>11.70757276145278</v>
       </c>
       <c r="D90" t="n">
-        <v>43.77681227884006</v>
+        <v>7.11373199531151</v>
       </c>
       <c r="E90" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F90" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3328,16 +3328,16 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>35.94482442026535</v>
+        <v>5.841033968293119</v>
       </c>
       <c r="D91" t="n">
-        <v>34.10301635038599</v>
+        <v>5.541740156937724</v>
       </c>
       <c r="E91" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F91" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>47.85428459460669</v>
+        <v>7.776321246623588</v>
       </c>
       <c r="D92" t="n">
-        <v>45.88874008502284</v>
+        <v>7.456920263816212</v>
       </c>
       <c r="E92" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F92" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3392,16 +3392,16 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>19.01169852899192</v>
+        <v>3.089401010961187</v>
       </c>
       <c r="D93" t="n">
-        <v>20.9085525012915</v>
+        <v>3.397639781459869</v>
       </c>
       <c r="E93" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F93" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3424,16 +3424,16 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>62.75540429368677</v>
+        <v>10.1977531977241</v>
       </c>
       <c r="D94" t="n">
-        <v>42.94034080629115</v>
+        <v>6.977805381022312</v>
       </c>
       <c r="E94" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F94" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3456,16 +3456,16 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>19.87843907908012</v>
+        <v>3.23024635035052</v>
       </c>
       <c r="D95" t="n">
-        <v>17.86765362635729</v>
+        <v>2.903493714283059</v>
       </c>
       <c r="E95" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F95" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3488,16 +3488,16 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>75.13755260515988</v>
+        <v>12.20985229833848</v>
       </c>
       <c r="D96" t="n">
-        <v>65.96200291104803</v>
+        <v>10.7188254730453</v>
       </c>
       <c r="E96" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F96" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>32.97687701158176</v>
+        <v>5.358742514382037</v>
       </c>
       <c r="D97" t="n">
-        <v>31.44487268085749</v>
+        <v>5.109791810639343</v>
       </c>
       <c r="E97" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F97" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3552,16 +3552,16 @@
         <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>52.85851865263271</v>
+        <v>8.589509281052816</v>
       </c>
       <c r="D98" t="n">
-        <v>50.79907259581776</v>
+        <v>8.254849296820387</v>
       </c>
       <c r="E98" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F98" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3584,16 +3584,16 @@
         <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>64.81966887526399</v>
+        <v>10.5331961922304</v>
       </c>
       <c r="D99" t="n">
-        <v>62.74592144288055</v>
+        <v>10.19621223446809</v>
       </c>
       <c r="E99" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F99" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3616,16 +3616,16 @@
         <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>6.33283845241117</v>
+        <v>1.029086248516815</v>
       </c>
       <c r="D100" t="n">
-        <v>7.534934711103061</v>
+        <v>1.224426890554247</v>
       </c>
       <c r="E100" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F100" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3648,16 +3648,16 @@
         <v>100</v>
       </c>
       <c r="C101" t="n">
-        <v>57.04157041327896</v>
+        <v>9.269255192157832</v>
       </c>
       <c r="D101" t="n">
-        <v>54.91031801332957</v>
+        <v>8.922926677166055</v>
       </c>
       <c r="E101" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F101" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3680,16 +3680,16 @@
         <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>71.43423016690586</v>
+        <v>11.6080624021222</v>
       </c>
       <c r="D102" t="n">
-        <v>56.79665325465653</v>
+        <v>9.229456153881685</v>
       </c>
       <c r="E102" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F102" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3712,16 +3712,16 @@
         <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>62.16449943241256</v>
+        <v>10.10173115776704</v>
       </c>
       <c r="D103" t="n">
-        <v>49.71611446125807</v>
+        <v>8.078868599954436</v>
       </c>
       <c r="E103" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F103" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3744,16 +3744,16 @@
         <v>103</v>
       </c>
       <c r="C104" t="n">
-        <v>49.70210645054122</v>
+        <v>8.076592298212947</v>
       </c>
       <c r="D104" t="n">
-        <v>43.66015683520601</v>
+        <v>7.094775485720977</v>
       </c>
       <c r="E104" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F104" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3776,16 +3776,16 @@
         <v>104</v>
       </c>
       <c r="C105" t="n">
-        <v>21.03430185612713</v>
+        <v>3.418074051620659</v>
       </c>
       <c r="D105" t="n">
-        <v>22.81959833697955</v>
+        <v>3.708184729759177</v>
       </c>
       <c r="E105" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F105" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>12.3987383380142</v>
+        <v>2.014794979927308</v>
       </c>
       <c r="D106" t="n">
-        <v>13.8830013693322</v>
+        <v>2.255987722516483</v>
       </c>
       <c r="E106" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F106" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3840,16 +3840,16 @@
         <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>6.284297596733295</v>
+        <v>1.02119835946916</v>
       </c>
       <c r="D107" t="n">
-        <v>4.120650606717537</v>
+        <v>0.6696057235915998</v>
       </c>
       <c r="E107" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F107" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3872,16 +3872,16 @@
         <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>12.89342546066814</v>
+        <v>2.095181637358572</v>
       </c>
       <c r="D108" t="n">
-        <v>10.83185412640622</v>
+        <v>1.76017629554101</v>
       </c>
       <c r="E108" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F108" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3904,16 +3904,16 @@
         <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>24.97626704367741</v>
+        <v>4.05864339459758</v>
       </c>
       <c r="D109" t="n">
-        <v>22.80908806910753</v>
+        <v>3.706476811229975</v>
       </c>
       <c r="E109" t="n">
-        <v>23.65268072331638</v>
+        <v>3.843560617538912</v>
       </c>
       <c r="F109" t="n">
-        <v>19.79387148584814</v>
+        <v>3.216504116450324</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
